--- a/协作/37-发布历史.xlsx
+++ b/协作/37-发布历史.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -532,10 +532,52 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>协议 v3.5（DCG 2.0.0 仍未发布）</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3f1aef4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tm-v3.5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>发布说明-0001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>回滚到 TEAMODEL-交付包-v3.4.zip / 标签 tm-v3.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>已发布</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"已发布,已回滚,已废弃"</formula1>
+    <dataValidation sqref="G2:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"未发布,已发布,已回滚,已废弃"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/协作/37-发布历史.xlsx
+++ b/协作/37-发布历史.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3f1aef4</t>
+          <t>77fb43c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>回滚到 TEAMODEL-交付包-v3.4.zip / 标签 tm-v3.4</t>
+          <t>回滚到 TEAMODEL-交付包-v3.4.zip / 标签 tm-v3.4（v3.5 无代码变更，回滚仅还原文档与模板）</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
